--- a/output/full_scan/batch_seq6_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1148.415306931256</v>
+        <v>1348.415306931256</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>29.75</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.49585132548725</v>
+        <v>66.49585123248428</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>40.96763774649993</v>
+        <v>40.96763761602286</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.841530693125586</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0464633694207887</v>
+        <v>0.0464633697260599</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>991.3304125651588</v>
+        <v>1281.330412565159</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>51.7</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.8803475448652</v>
+        <v>68.88034752504288</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>37.046122804598</v>
+        <v>37.0461228229429</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.633041256515869</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.1264260434478732</v>
+        <v>-0.1264260434383399</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6173</v>
+        <v>6244</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>860</v>
+        <v>1172.282771627206</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>251.5</v>
+        <v>31.25</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.10562145783457</v>
+        <v>56.7895005816837</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>47.35127241856723</v>
+        <v>21.18694522846976</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.94242885295773</v>
+        <v>3.228277162720614</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-1.778679292935056</v>
+        <v>0.0454156252924228</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6244</v>
+        <v>6173</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>837.2827716272061</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31.25</v>
+        <v>251.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.7895005940796</v>
+        <v>73.1056214496631</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.18694522208474</v>
+        <v>47.35127237858507</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.228277162720614</v>
+        <v>10.94242885295773</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0454156253305843</v>
+        <v>-1.778679292915989</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6465</v>
+        <v>6227</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>835.5368542845968</v>
+        <v>1010.072396187502</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55.4</v>
+        <v>130.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.85862755764698</v>
+        <v>58.89057806767249</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.06074647408062</v>
+        <v>34.37088449818663</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.553685428459681</v>
+        <v>0.5072396187502183</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0780115877287164</v>
+        <v>-1.249738379164883</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6227</v>
+        <v>6414</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>780.0723961875021</v>
+        <v>989.3133526022924</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>130.5</v>
+        <v>395</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.89057815738998</v>
+        <v>63.89794227725616</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.37088448386856</v>
+        <v>35.43618292554701</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5072396187502183</v>
+        <v>0.9313352602292524</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.249738379203043</v>
+        <v>1.303564280742139</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6175</v>
+        <v>6196</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>743.3820155122467</v>
+        <v>983.9683860704243</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>103</v>
+        <v>504</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.87794754634022</v>
+        <v>62.72071279914611</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45.55637614477298</v>
+        <v>43.82164900991311</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.338201551224669</v>
+        <v>0.8968386070424454</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.212075238553993</v>
+        <v>-3.135853689452041</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6414</v>
+        <v>6177</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>719.1028049577964</v>
+        <v>980.5832098041184</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>395</v>
+        <v>47.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.89794226723378</v>
+        <v>63.81701962076547</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.43618292554701</v>
+        <v>17.9999394223039</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9102804957796315</v>
+        <v>2.058320980411836</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.303564281219135</v>
+        <v>0.4933266952657056</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6265</v>
+        <v>6465</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>718.5738408232728</v>
+        <v>950.5368542845968</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>57.7</v>
+        <v>55.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.0923851364524</v>
+        <v>58.85862755543533</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.77173375213609</v>
+        <v>15.06074660505127</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8573840823272767</v>
+        <v>1.553685428459681</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1663357944912116</v>
+        <v>0.0780115876633222</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6196</v>
+        <v>6175</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>718.4829479361874</v>
+        <v>943.3820155122468</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>504</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62.72071281437145</v>
+        <v>65.8779475211947</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>43.82164901788328</v>
+        <v>45.55637620698381</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8482947936187394</v>
+        <v>1.338201551224669</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-3.135853689261246</v>
+        <v>-0.2120752384872197</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>701.6899138608945</v>
+        <v>891.9751074754925</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>317.5</v>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.2452789099472</v>
+        <v>66.24527889258144</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.7247712955087</v>
+        <v>52.72477131222024</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.168991386089452</v>
+        <v>1.19751074754924</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.197267990743846</v>
+        <v>1.197267990457654</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6204</v>
+        <v>6239</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>701.612164385782</v>
+        <v>891.0982375412848</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>105</v>
+        <v>333</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.89374958055225</v>
+        <v>58.67689936361401</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>47.07396116101366</v>
+        <v>31.934714095046</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.1612164385782</v>
+        <v>0.6098237541284782</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.6372085240514238</v>
+        <v>-4.876029654930235</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6177</v>
+        <v>6166</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>695.4416450827846</v>
+        <v>888.4653578384458</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>47.4</v>
+        <v>128</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.81701971158174</v>
+        <v>58.62091858719095</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17.99993938241838</v>
+        <v>63.68073985110014</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.044164508278455</v>
+        <v>0.8465357838445823</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4933266951607728</v>
+        <v>-2.061751310067724</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6290</v>
+        <v>6241</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>689.0765893196863</v>
+        <v>885.90258169039</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>296.5</v>
+        <v>12.65</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45.94417894813358</v>
+        <v>72.63424452415828</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.68212463062288</v>
+        <v>18.50482918724078</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.9076589319686234</v>
+        <v>2.090258169038992</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-6.782238201575165</v>
+        <v>0.2202364663484127</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6241</v>
+        <v>6223</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>685.90258169039</v>
+        <v>884.914809320329</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.65</v>
+        <v>6090</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>72.63424464296349</v>
+        <v>57.32677352459179</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.50482916185675</v>
+        <v>20.89025651235518</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.090258169038992</v>
+        <v>0.9914809320329068</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2202364663007138</v>
+        <v>-54.58455970552376</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6220</v>
+        <v>6204</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>659.0656963067345</v>
+        <v>841.612164385782</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>34.5</v>
+        <v>105</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.62869006499731</v>
+        <v>61.89374955824726</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45.5583369623408</v>
+        <v>47.07396115979628</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.40656963067345</v>
+        <v>1.1612164385782</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1787350195519471</v>
+        <v>0.6372085244902621</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6166</v>
+        <v>6409</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>648.3711492413165</v>
+        <v>831.1380044493505</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>128</v>
+        <v>846</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.62091861827748</v>
+        <v>58.71154603148208</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>63.68073982600616</v>
+        <v>31.85238145287832</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8371149241316548</v>
+        <v>0.613800444935057</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.06175131031576</v>
+        <v>18.06400362902063</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6446</v>
+        <v>6411</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>647.7908093092528</v>
+        <v>828.2046931904798</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>934</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.96875811613177</v>
+        <v>51.76597191537371</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42.40099983141597</v>
+        <v>30.20927725374609</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.279080930925286</v>
+        <v>0.3204693190479826</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.134227427764131</v>
+        <v>-1.622226724716576</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6207</v>
+        <v>6432</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>645.7879354466464</v>
+        <v>822.0245912913258</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>125</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.15154862119524</v>
+        <v>67.36795197979464</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>63.32212937581534</v>
+        <v>45.99913638367266</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.078793544664646</v>
+        <v>1.202459129132579</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0216661259973669</v>
+        <v>0.4232803923448838</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6257</v>
+        <v>6220</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>644.6505849233957</v>
+        <v>799.0656963067345</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>205.5</v>
+        <v>34.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46.75149475850952</v>
+        <v>59.62869005075884</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.28512683706054</v>
+        <v>45.55833694005165</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.46505849233957</v>
+        <v>1.40656963067345</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-4.392157058667242</v>
+        <v>0.1787350195901046</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6285</v>
+        <v>6405</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>642.2004807176497</v>
+        <v>793.7389102430527</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>272.5</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>47.66583719794994</v>
+        <v>58.76065807573648</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.69516547313899</v>
+        <v>46.33402303783354</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7200480717649683</v>
+        <v>0.373891024305275</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-6.570553764704449</v>
+        <v>-1.361003342800754</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6435</v>
+        <v>6446</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>639.7167316269871</v>
+        <v>788.4239474239647</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>258</v>
+        <v>934</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.53650555802658</v>
+        <v>61.96875809173045</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.83353342197624</v>
+        <v>42.40099983141597</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4716731626987082</v>
+        <v>1.342394742396474</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-4.693407876752637</v>
+        <v>1.134227428622744</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6411</v>
+        <v>6270</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>638.2046931904798</v>
+        <v>761.1512237381843</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.76597194511125</v>
+        <v>66.67433980246534</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>30.20927724605056</v>
+        <v>41.62159476893832</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3204693190479826</v>
+        <v>1.615122373818431</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,11 +1736,11 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.622226724716576</v>
+        <v>0.9610960318723744</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>637.9319556333801</v>
+        <v>752.9319556333801</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>58.9</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.30217657819254</v>
+        <v>53.30217657252791</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.04661031438618</v>
+        <v>34.04661027789931</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.2931955633380098</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.9416103266180365</v>
+        <v>-0.9416103266943492</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6271</v>
+        <v>6285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>624.496026542743</v>
+        <v>737.3179238379688</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>217</v>
+        <v>272.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.25344716129121</v>
+        <v>47.66583718805367</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.05710267406331</v>
+        <v>32.69516548040875</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9496026542742984</v>
+        <v>0.7317923837968798</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-4.147403251505484</v>
+        <v>-6.570553764799845</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6432</v>
+        <v>6225</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>622.0245912913258</v>
+        <v>735.4813352590315</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>23.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.36795199177351</v>
+        <v>44.46689194052329</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45.99913633984309</v>
+        <v>16.42133143966042</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.202459129132579</v>
+        <v>1.048133525903158</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4232803923162658</v>
+        <v>-0.4652962149427379</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6223</v>
+        <v>6279</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>619.914809320329</v>
+        <v>735.1891343828164</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6090</v>
+        <v>120.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.32677353140996</v>
+        <v>54.80182622615808</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.89025653114561</v>
+        <v>23.22661111680953</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9914809320329068</v>
+        <v>0.5189134382816454</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-54.58455970571504</v>
+        <v>-0.1624010051893325</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6263</v>
+        <v>6210</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>607.8924911461869</v>
+        <v>720.2610099521557</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>156</v>
+        <v>20.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>42.88560137983122</v>
+        <v>49.84686814316875</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23.6416134703168</v>
+        <v>21.88931560720374</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7892491146186896</v>
+        <v>0.5261009952155722</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-4.192300789170009</v>
+        <v>-0.0509718936306795</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6190</v>
+        <v>6265</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>580.3916613035908</v>
+        <v>718.5738408232728</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79</v>
+        <v>57.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.23458691157224</v>
+        <v>59.09238513530487</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>36.46536492488014</v>
+        <v>35.77173377001571</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5391661303590832</v>
+        <v>0.8573840823272767</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.189809023425173</v>
+        <v>-0.1663357945083881</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6415</v>
+        <v>6190</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>579.6190889109708</v>
+        <v>695.3916613035908</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.63451247905933</v>
+        <v>50.23458686777415</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.67338277939469</v>
+        <v>36.4653648798632</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9619088910970834</v>
+        <v>0.5391661303590832</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-20.68960192354385</v>
+        <v>-1.189809023329772</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6274</v>
+        <v>6464</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>574.3827911366654</v>
+        <v>691.8272567477046</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1475</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.64979309154413</v>
+        <v>60.85130909436173</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.30235772953987</v>
+        <v>15.22162360381354</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.438279113666553</v>
+        <v>0.1827256747704596</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-33.98418345842924</v>
+        <v>-0.0479388639685878</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6209</v>
+        <v>6189</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>567.4195401095917</v>
+        <v>691.5966702037497</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>79.3</v>
+        <v>52.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.87063768495826</v>
+        <v>53.28475182299694</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>33.42036591261865</v>
+        <v>27.86428693186837</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7419540109591678</v>
+        <v>0.6596670203749635</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.7939854406289264</v>
+        <v>0.06697390549970619</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6282</v>
+        <v>6290</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>567.3674721707381</v>
+        <v>689.0765893196863</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>57.2</v>
+        <v>296.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.09849255948939</v>
+        <v>45.9441789370609</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>33.78442958057844</v>
+        <v>23.68212463185701</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7367472170738082</v>
+        <v>0.9076589319686234</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,11 +2266,11 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.6901812377809744</v>
+        <v>-6.782238201460661</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>566.7032153303896</v>
+        <v>681.7032153303896</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>82.40000000000001</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.78528449457355</v>
+        <v>44.78528441241043</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.44615456673404</v>
+        <v>26.4461545498784</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6703215330389644</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.9344766086794118</v>
+        <v>-0.9344766086603208</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6279</v>
+        <v>6214</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>565.1891343828165</v>
+        <v>681.5179181638528</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>120.5</v>
+        <v>142</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.80182607651984</v>
+        <v>58.84311866123358</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.2266110788219</v>
+        <v>29.56488560416239</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5189134382816454</v>
+        <v>0.6517918163852713</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,11 +2372,11 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1624010049985378</v>
+        <v>0.0470365783037873</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>563.8366151097184</v>
+        <v>678.8366151097184</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>132.5</v>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.68015946061595</v>
+        <v>48.6801594437644</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.81857253730842</v>
+        <v>24.81857262598859</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.3836615109718466</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.73468798443441</v>
+        <v>-1.73468798435809</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6270</v>
+        <v>6224</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>561.1512237381843</v>
+        <v>663.5879824149923</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>35.2</v>
+        <v>76.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>66.67433987739307</v>
+        <v>48.07735112721742</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>41.62159494456365</v>
+        <v>32.16926733251743</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.615122373818431</v>
+        <v>0.8587982414992351</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.9610960316911196</v>
+        <v>-1.765621088740945</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6214</v>
+        <v>6443</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>556.4024398080692</v>
+        <v>662.6314087419215</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.84311874054461</v>
+        <v>49.14421183836877</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.56488560632892</v>
+        <v>22.39894210053522</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.640243980806917</v>
+        <v>1.763140874192151</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0470365781129586</v>
+        <v>-0.2348081075757761</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6443</v>
+        <v>6282</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>547.5478352609312</v>
+        <v>647.4246374771571</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>40</v>
+        <v>57.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.14421185924889</v>
+        <v>49.09849254680381</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.39894209742309</v>
+        <v>33.78442960547709</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.754783526093116</v>
+        <v>0.7424637477157129</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2348081075662282</v>
+        <v>-0.6901812378668377</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6451</v>
+        <v>6207</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>546.3174251516352</v>
+        <v>645.7879354466464</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>499.5</v>
+        <v>125</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.0686467237416</v>
+        <v>60.15154860495231</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>38.30300031047607</v>
+        <v>63.32212938675089</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.131742515163519</v>
+        <v>1.078793544664646</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-15.55297523378509</v>
+        <v>-0.021666125835182</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6464</v>
+        <v>6435</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>541.8132822927947</v>
+        <v>639.7167316269871</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>60.85130976397193</v>
+        <v>52.53650553286835</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.22162357676949</v>
+        <v>30.83353348346634</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1813282292794721</v>
+        <v>0.4716731626987082</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0479388640449004</v>
+        <v>-4.693407876619101</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6189</v>
+        <v>6257</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>531.5342278929123</v>
+        <v>629.751520868632</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>52.3</v>
+        <v>205.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.28475186630251</v>
+        <v>46.75149474183059</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.86428696663437</v>
+        <v>33.28512685536492</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6534227892912355</v>
+        <v>0.4751520868632098</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.06697390565233929</v>
+        <v>-4.39215705859093</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6269</v>
+        <v>6472</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>528.8275847160277</v>
+        <v>628.4440619663293</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>65.8</v>
+        <v>380.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.46965726473808</v>
+        <v>49.87465615352598</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24.43363567286397</v>
+        <v>22.58652691928198</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8827584716027672</v>
+        <v>0.8444061966329288</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.08367582155549839</v>
+        <v>6.183049129216506</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6224</v>
+        <v>6271</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>528.5269732959737</v>
+        <v>624.6805837041632</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>76.3</v>
+        <v>217</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.07735113795867</v>
+        <v>49.25344714281162</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>32.16926731959362</v>
+        <v>34.05710264438461</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8526973295973759</v>
+        <v>0.9680583704163104</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,84 +2849,84 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.765621088750479</v>
+        <v>-4.147403251295612</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6288</v>
+        <v>6412</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>526.8310325240927</v>
+        <v>620.821195952836</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>20.95</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.44696382882753</v>
+        <v>46.24786788338061</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.37340261095357</v>
+        <v>31.25565867414411</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>1.082119595283593</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0429088447259439</v>
+        <v>-2.08846475963833</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6277</v>
+        <v>6419</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>520.4720675644282</v>
+        <v>612.5478906084376</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>73.2</v>
+        <v>140</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45.2619948798141</v>
+        <v>49.01356576779376</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>44.95884160184971</v>
+        <v>19.34381097206465</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5472067564428162</v>
+        <v>0.2547890608437566</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.7406289101322512</v>
+        <v>-2.860351902415379</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6237</v>
+        <v>6263</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>512.1711952927992</v>
+        <v>607.8924911461869</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>43.35</v>
+        <v>156</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.46688652226356</v>
+        <v>42.88560133409554</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>34.41984439701604</v>
+        <v>23.64161348119404</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2171195292799179</v>
+        <v>0.7892491146186896</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.390756974537408</v>
+        <v>-4.192300788979217</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6412</v>
+        <v>6237</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>510.7310966842947</v>
+        <v>602.1711952927992</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>43.35</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.24786796718842</v>
+        <v>41.46688648629839</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>31.25565854525507</v>
+        <v>34.419844439786</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.073109668429474</v>
+        <v>0.2171195292799179</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.088464759924523</v>
+        <v>-1.390756974546948</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6283</v>
+        <v>6277</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>500.6233449846415</v>
+        <v>600.5215124979288</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>23.15</v>
+        <v>73.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.67792501235041</v>
+        <v>45.26199489500185</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.24027280552584</v>
+        <v>44.95884154811777</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.562334498464146</v>
+        <v>0.5521512497928747</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,11 +3114,11 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.2101774581797019</v>
+        <v>-0.74062891022764</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>499.4289289016234</v>
+        <v>599.5521917328994</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>132</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.81596600048068</v>
+        <v>49.81596595684285</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>30.91040277260365</v>
+        <v>30.91040275912745</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9428928901623344</v>
+        <v>0.9552191732899356</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.982996177022478</v>
+        <v>-1.982996177308674</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6409</v>
+        <v>6415</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>495.8167009747219</v>
+        <v>589.8132001004742</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>846</v>
+        <v>481</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>58.71154601018775</v>
+        <v>43.63451252721352</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.85238145287832</v>
+        <v>33.67338279578703</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5816700974721876</v>
+        <v>0.9813200100474172</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>18.06400363283645</v>
+        <v>-20.6896019294585</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6225</v>
+        <v>6278</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>495.4732572682578</v>
+        <v>587.8325795564433</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>23.1</v>
+        <v>192</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.46689203076306</v>
+        <v>45.42890778667669</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.42133142746003</v>
+        <v>25.16528094415769</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.047325726825787</v>
+        <v>0.7832579556443329</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.4652962150095153</v>
+        <v>-7.075644161366609</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6208</v>
+        <v>6198</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>492.2268555713149</v>
+        <v>586.0883406070764</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>79</v>
+        <v>20.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.31484576690085</v>
+        <v>51.28773924429927</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.70505743651136</v>
+        <v>9.856394594819406</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2226855571314855</v>
+        <v>0.108834060707639</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.81669160265075</v>
+        <v>0.1562394558127835</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6210</v>
+        <v>6234</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>490.2610099521557</v>
+        <v>584.2110094266086</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>20.9</v>
+        <v>43.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.84686823486715</v>
+        <v>43.47786660029065</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.88931590459613</v>
+        <v>22.56939154438031</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5261009952155722</v>
+        <v>0.4211009426608637</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0509718936974598</v>
+        <v>-1.078962979170271</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6278</v>
+        <v>6274</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>477.7767579779724</v>
+        <v>574.3827911366654</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>192</v>
+        <v>1475</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.42890778372376</v>
+        <v>51.64979308752707</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.16528093855738</v>
+        <v>32.30235776529351</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7776757977972324</v>
+        <v>1.438279113666553</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-7.075644160985004</v>
+        <v>-33.98418345871562</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6419</v>
+        <v>6209</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>472.5478906084376</v>
+        <v>567.4871915940616</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>140</v>
+        <v>79.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.01356578265028</v>
+        <v>51.87063767321334</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.34381091292835</v>
+        <v>33.42036593884773</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2547890608437566</v>
+        <v>0.7487191594061614</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-2.860351902186426</v>
+        <v>-0.7939854406193811</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6205</v>
+        <v>6451</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>470.0832329013211</v>
+        <v>566.6454770657651</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>78.7</v>
+        <v>499.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.69379501098648</v>
+        <v>44.06864671740203</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.92948041434157</v>
+        <v>38.30300031047607</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5083232901321123</v>
+        <v>1.164547706576517</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.92990109478408</v>
+        <v>-15.55297523388047</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6234</v>
+        <v>6284</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>469.2110094266087</v>
+        <v>557.3767446135623</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>43.9</v>
+        <v>96.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.47786662394852</v>
+        <v>47.84349743562709</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.56939154088668</v>
+        <v>42.36270655470309</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4211009426608637</v>
+        <v>0.7376744613562297</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.078962979179812</v>
+        <v>-2.160556172738081</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6485</v>
+        <v>6431</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>光麗-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>463.1953065362045</v>
+        <v>550.7064880200028</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>85</v>
+        <v>18.65</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.57661136284464</v>
+        <v>42.93571742764966</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>27.23775191135424</v>
+        <v>21.49690789601601</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3195306536204413</v>
+        <v>2.070648802000279</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-3.714122197636072</v>
+        <v>-0.1064769555224939</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6431</v>
+        <v>6474</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>光麗-KY</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>450.7059538555157</v>
+        <v>548.0292762067377</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>18.65</v>
+        <v>37.95</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.93571749464745</v>
+        <v>50.29119843308845</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.49690786443127</v>
+        <v>19.04655731632598</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.070595385551564</v>
+        <v>0.3029276206737723</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1064769555224939</v>
+        <v>-0.1073681546354592</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, williams_r_recovery</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6284</v>
+        <v>6165</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>442.3767446135623</v>
+        <v>535.891467197634</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>96.7</v>
+        <v>48.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.84349747392465</v>
+        <v>47.77860798348528</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>42.36270653898766</v>
+        <v>20.51642618066596</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7376744613562297</v>
+        <v>0.5891467197634008</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.160556172757172</v>
+        <v>-0.0039174303449579</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6462</v>
+        <v>6228</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>433.8111706475384</v>
+        <v>532.4977218970519</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>110</v>
+        <v>21.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.78498875248697</v>
+        <v>50.78990387697337</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.0437537409333</v>
+        <v>2.801435125722143</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3811170647538407</v>
+        <v>0.7497721897051853</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,51 +3803,51 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.127219355257893</v>
+        <v>0.0571895724951126</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6423</v>
+        <v>6288</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>430.4362496842257</v>
+        <v>526.8310325240927</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>80</v>
+        <v>20.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>28.26818401985956</v>
+        <v>51.20701232738176</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.81631350613836</v>
+        <v>23.25831693858013</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.543624968422572</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.765155905951776</v>
+        <v>0.0424721831038517</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6192</v>
+        <v>6170</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>429.9810542893217</v>
+        <v>519.5749378978635</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>117.5</v>
+        <v>51.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>36.97850928557941</v>
+        <v>51.27129300631226</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.32298465755968</v>
+        <v>20.87744491172256</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3.498105428932164</v>
+        <v>1.457493789786346</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.088059816941044</v>
+        <v>0.0848476232617662</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6198</v>
+        <v>6213</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>416.0883406070764</v>
+        <v>512.2742482218055</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>20.6</v>
+        <v>248</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.28773885260952</v>
+        <v>45.92572620239944</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.856394401508387</v>
+        <v>18.6259845479656</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.108834060707639</v>
+        <v>0.7274248221805457</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1562394623474958</v>
+        <v>-3.67593830276693</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6474</v>
+        <v>6205</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>408.0292762067377</v>
+        <v>510.1296261537203</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>37.95</v>
+        <v>78.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.29119843308845</v>
+        <v>47.69379496959554</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.04655731632598</v>
+        <v>19.92948039780813</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3029276206737723</v>
+        <v>0.512962615372033</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1073681546354592</v>
+        <v>-0.9299010947077612</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6261</v>
+        <v>6269</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>401.9306790871881</v>
+        <v>508.9239594111911</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.5</v>
+        <v>65.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>36.26932955098894</v>
+        <v>50.46965724945345</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.70317889771202</v>
+        <v>24.43363568118712</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6930679087188055</v>
+        <v>0.8923959411191111</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-3.607825336968089</v>
+        <v>0.083675821488699</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6165</v>
+        <v>6208</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>395.8659917480656</v>
+        <v>492.2268555713149</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>48.4</v>
+        <v>79</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.77860794613308</v>
+        <v>42.31484574341889</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.51642618066596</v>
+        <v>30.7050574244048</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5865991748065541</v>
+        <v>0.2226855571314855</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0039174302495672</v>
+        <v>-2.816691602479035</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6213</v>
+        <v>6261</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>387.137133971194</v>
+        <v>491.9306790871881</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>248</v>
+        <v>94.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.92572621166241</v>
+        <v>36.26932953909969</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.6259845479656</v>
+        <v>22.70317888505954</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7137133971193986</v>
+        <v>0.6930679087188055</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-3.675938302805093</v>
+        <v>-3.607825336872701</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6170</v>
+        <v>6194</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>379.5749378978635</v>
+        <v>485.867304987076</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>51.7</v>
+        <v>32.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.27129323024168</v>
+        <v>43.26335131502861</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.87744495418118</v>
+        <v>21.7686925410238</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.457493789786346</v>
+        <v>0.0867304987075951</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0848476233285429</v>
+        <v>-0.2438242529622428</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6418</v>
+        <v>6283</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>371.4400783104292</v>
+        <v>480.652390326172</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>31.85</v>
+        <v>23.15</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.52865888589463</v>
+        <v>41.67792495986176</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.6076282906673</v>
+        <v>22.2402728456152</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6440078310429159</v>
+        <v>1.5652390326172</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1418868678534072</v>
+        <v>-0.2101774581510844</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6272</v>
+        <v>6184</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>371.2577750905362</v>
+        <v>476.9050373924086</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>35.1</v>
+        <v>46.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.90194891784422</v>
+        <v>52.79737431719285</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>34.4018247982037</v>
+        <v>20.9491874988039</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6257775090536225</v>
+        <v>0.6905037392408635</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0062493753785171</v>
+        <v>0.082628465583773</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6194</v>
+        <v>6485</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>370.867304987076</v>
+        <v>463.1953065362045</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>32.5</v>
+        <v>85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.26335142170183</v>
+        <v>39.57661134615644</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.76869246958803</v>
+        <v>27.23775190886942</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.0867304987075951</v>
+        <v>0.3195306536204413</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.24382425302902</v>
+        <v>-3.714122197521584</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6228</v>
+        <v>6477</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>362.4977218970519</v>
+        <v>461.626227778576</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>21.6</v>
+        <v>33.85</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.78990404083317</v>
+        <v>50.24199794465257</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2.801435080768933</v>
+        <v>16.14752884818024</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7497721897051853</v>
+        <v>2.162622777857603</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0571895723520174</v>
+        <v>-0.1008889875925694</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6477</v>
+        <v>6229</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>361.4948460791866</v>
+        <v>453.6477686473618</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>33.85</v>
+        <v>26.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.24199799047057</v>
+        <v>47.51376540704515</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.14752884464982</v>
+        <v>17.6292111507892</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.149484607918654</v>
+        <v>0.8647768647361801</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1008889875448717</v>
+        <v>-0.2072575653128768</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6472</v>
+        <v>6222</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>358.064182138788</v>
+        <v>439.3906457661988</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>380.5</v>
+        <v>20.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.87465627076662</v>
+        <v>38.88521877547246</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.58652692100512</v>
+        <v>28.13041855559362</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8064182138787984</v>
+        <v>0.9390645766198772</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>6.183049129216506</v>
+        <v>-0.0547840057878888</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6184</v>
+        <v>6462</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>356.7774401608513</v>
+        <v>433.8111706475384</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46.6</v>
+        <v>110</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.79737431719285</v>
+        <v>37.78498876180034</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.94918738920569</v>
+        <v>25.04375370859012</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6777440160851246</v>
+        <v>0.3811170647538407</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.082628465602853</v>
+        <v>-3.127219355849358</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6235</v>
+        <v>6423</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>355.1636430887635</v>
+        <v>430.4362496842257</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>40.2</v>
+        <v>80</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>39.86729336250944</v>
+        <v>28.26818409105326</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>23.44726169944645</v>
+        <v>22.8163134503891</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5163643088763478</v>
+        <v>1.543624968422572</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1910329011536479</v>
+        <v>-1.76515590543664</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6426</v>
+        <v>6176</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>343.6572830494778</v>
+        <v>421.1877523540696</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>195.5</v>
+        <v>91.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>35.91726866328419</v>
+        <v>36.06613627512376</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.96830023478838</v>
+        <v>30.15204849982436</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8657283049477792</v>
+        <v>1.118775235406963</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-9.395596702106428</v>
+        <v>-1.78255762930039</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6438</v>
+        <v>6281</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>341.5183257077496</v>
+        <v>414.5846941358762</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>144</v>
+        <v>51.4</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>27.54141161219061</v>
+        <v>50.44543369824947</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.62730707654177</v>
+        <v>16.99038672968553</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6518325707749559</v>
+        <v>0.9584694135876172</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-2.627525624109025</v>
+        <v>0.1809668628704649</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6176</v>
+        <v>6187</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>341.0882252077535</v>
+        <v>413.6258546815152</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91.7</v>
+        <v>1030</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>36.06613629133879</v>
+        <v>44.54957149290185</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>30.15204852221653</v>
+        <v>13.74308439534533</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.108822520775343</v>
+        <v>0.8625854681515138</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.782557628823412</v>
+        <v>-11.38072455864976</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6229</v>
+        <v>6470</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>338.6477686473618</v>
+        <v>393.6950453237601</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>26.2</v>
+        <v>48.3</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.51376552224655</v>
+        <v>48.1423499266357</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.62921112056121</v>
+        <v>15.89318968129835</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8647768647361801</v>
+        <v>1.36950453237601</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2072575653414981</v>
+        <v>-0.0006575902048681</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6215</v>
+        <v>6246</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>337.4647007775259</v>
+        <v>385.8442294197979</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>107</v>
+        <v>15.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.90827276587611</v>
+        <v>44.6820234365971</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.9400928604416</v>
+        <v>16.26995018435079</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.2464700777525922</v>
+        <v>0.5844229419797891</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-2.748577993498956</v>
+        <v>-0.0149177261685519</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6217</v>
+        <v>6235</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>332.2602517871118</v>
+        <v>385.2331668129695</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>228</v>
+        <v>40.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.51201954977564</v>
+        <v>39.86729329811141</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.27471429441228</v>
+        <v>23.44726172998245</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.226025178711182</v>
+        <v>0.5233166812969507</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-8.235621491412802</v>
+        <v>-0.1910329012204222</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6275</v>
+        <v>6418</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>330.1121260055042</v>
+        <v>371.4400783104292</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>46.85</v>
+        <v>31.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.83403955765021</v>
+        <v>51.52865888037039</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20.01658168666198</v>
+        <v>22.60762837505239</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5112126005504219</v>
+        <v>0.6440078310429159</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.227151922643665</v>
+        <v>0.1418868678247887</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6168</v>
+        <v>6272</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>327.2699527566296</v>
+        <v>371.3163452887134</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>24.1</v>
+        <v>35.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.57405767429823</v>
+        <v>50.90194873146011</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.01581645601076</v>
+        <v>34.40182488326288</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2269952756629602</v>
+        <v>0.6316345288713346</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.52931838659886</v>
+        <v>-0.0062493751400287</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6164</v>
+        <v>6183</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>323.8595782215523</v>
+        <v>364.5506265171032</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12.2</v>
+        <v>88.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.28428805882385</v>
+        <v>28.31876759582084</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.34924020564074</v>
+        <v>22.96898607142844</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8859578221552333</v>
+        <v>0.9550626517103188</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0241932587825133</v>
+        <v>-0.2278271401123877</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6202</v>
+        <v>6426</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>320.5961737902141</v>
+        <v>363.7727428347843</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>54</v>
+        <v>195.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.09316496672373</v>
+        <v>35.91726865854716</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.13024605239363</v>
+        <v>21.96830017088682</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.059617379021413</v>
+        <v>0.8772742834784309</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.8728162696351899</v>
+        <v>-9.395596701782052</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>318.6258546815151</v>
+        <v>360.4822870951584</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1030</v>
+        <v>117.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.54957150575393</v>
+        <v>36.97850922276105</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.7430843973897</v>
+        <v>22.32298467700634</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8625854681515138</v>
+        <v>3.548228709515844</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-11.38072455807739</v>
+        <v>-1.088059816750254</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6216</v>
+        <v>6201</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>299.7405156253831</v>
+        <v>356.3745154993374</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>22.4</v>
+        <v>47</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>39.61172688424172</v>
+        <v>36.81080851002381</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>23.8305726821865</v>
+        <v>25.10058847545666</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.974051562538306</v>
+        <v>1.137451549933742</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0451602599794592</v>
+        <v>-0.06874608706709361</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6222</v>
+        <v>6438</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>299.3906457661988</v>
+        <v>341.7505078592853</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20.2</v>
+        <v>144</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.88521877547246</v>
+        <v>27.5414115297914</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>28.13041855928726</v>
+        <v>23.62730711179842</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9390645766198772</v>
+        <v>0.6750507859285362</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0547840057878888</v>
+        <v>-2.627525624490609</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6226</v>
+        <v>6215</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>276.6859566103213</v>
+        <v>337.5089093533553</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>11.9</v>
+        <v>107</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.07169236420873</v>
+        <v>38.90827259501605</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.9475215110135</v>
+        <v>20.9400928217486</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.168595661032134</v>
+        <v>0.250890935335524</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1453771499317606</v>
+        <v>-2.748577992048917</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6246</v>
+        <v>6217</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>270.8442294197979</v>
+        <v>332.2602517871118</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>15.25</v>
+        <v>228</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.68202340531387</v>
+        <v>40.51201954836328</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.26995024278882</v>
+        <v>16.274714335886</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5844229419797891</v>
+        <v>1.226025178711182</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0149177261590127</v>
+        <v>-8.235621491384224</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6230</v>
+        <v>6275</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>267.81941727175</v>
+        <v>330.1121260055042</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>131.5</v>
+        <v>46.85</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.12968305792256</v>
+        <v>39.83403951566486</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.12834220090168</v>
+        <v>20.01658172334412</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7819417271750025</v>
+        <v>0.5112126005504219</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.07615570348785811</v>
+        <v>-0.2271519227008974</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6281</v>
+        <v>6185</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>264.4849492896527</v>
+        <v>323.7980876203906</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>51.4</v>
+        <v>14</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.44543400129093</v>
+        <v>48.11869611051023</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.99038639930476</v>
+        <v>17.22783538426842</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9484949289652748</v>
+        <v>0.8798087620390626</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1809668626033517</v>
+        <v>0.0098914502432055</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6416</v>
+        <v>6202</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>254.7479458240198</v>
+        <v>320.6856277511339</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>81.8</v>
+        <v>54</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.03593973607461</v>
+        <v>46.09316491451277</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>30.59919860758403</v>
+        <v>17.13024609217392</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4747945824019786</v>
+        <v>1.068562775113387</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.315682241365002</v>
+        <v>-0.8728162695970301</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6266</v>
+        <v>6168</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>250.0705068016481</v>
+        <v>307.281046433574</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>25.35</v>
+        <v>24.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>27.63340776002539</v>
+        <v>39.57405766180175</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.24031597599076</v>
+        <v>18.0158164645397</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.507050680164816</v>
+        <v>0.2281046433573986</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1371326780126934</v>
+        <v>-0.5293183865893203</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6243</v>
+        <v>6216</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>246.3501471117414</v>
+        <v>299.8068892738413</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>30.15</v>
+        <v>22.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.90959135634892</v>
+        <v>39.61172669866038</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26.83691573061348</v>
+        <v>23.83057279694297</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6350147111741422</v>
+        <v>0.9806889273841298</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.5833941008740287</v>
+        <v>0.045160260046238</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6191</v>
+        <v>6416</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>245.8942404073412</v>
+        <v>294.80788108848</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>92</v>
+        <v>81.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.84791080253364</v>
+        <v>39.03593968322048</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.3619549952087</v>
+        <v>30.59919858941347</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5894240407341164</v>
+        <v>0.4807881088480057</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2875173373624267</v>
+        <v>-1.315682241536714</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6201</v>
+        <v>6164</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>241.1123698716233</v>
+        <v>273.8994476597782</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>47</v>
+        <v>12.2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.8108086759569</v>
+        <v>46.2842879962513</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>25.10058847545666</v>
+        <v>17.34924022303559</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.111236987162327</v>
+        <v>0.8899447659778238</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,48 +5817,48 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.068746087143414</v>
+        <v>-0.0241932587729739</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6287</v>
+        <v>6230</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>228.8193640139415</v>
+        <v>267.9940468604567</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>131.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>55.16749044366132</v>
+        <v>39.12968297528207</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4.238980300236367</v>
+        <v>14.12834218777554</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.7994046860456721</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0147397072979914</v>
+        <v>-0.07615570358324671</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6183</v>
+        <v>6266</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>223.9974214208156</v>
+        <v>250.0705068016481</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>88.7</v>
+        <v>25.35</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>28.31876780094452</v>
+        <v>27.63340770332034</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.96898607038306</v>
+        <v>20.24031596917218</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8997421420815535</v>
+        <v>1.507050680164816</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2278271402459408</v>
+        <v>-0.137132677984072</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6203</v>
+        <v>6243</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>213.8791811368409</v>
+        <v>246.4389101072644</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>30.15</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.99645265380238</v>
+        <v>36.90959133146315</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>23.14609784508443</v>
+        <v>26.83691575299345</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.887918113684089</v>
+        <v>0.6438910107264425</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.6149608490932026</v>
+        <v>-0.5833941009026473</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6185</v>
+        <v>6226</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>208.7980876203906</v>
+        <v>236.7369224313337</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14</v>
+        <v>11.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.11869624663094</v>
+        <v>41.07169235197477</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.22783547258915</v>
+        <v>17.94752148448322</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8798087620390626</v>
+        <v>1.173692243133371</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.009891450252744899</v>
+        <v>-0.1453771499317606</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6470</v>
+        <v>6191</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>203.6950453237601</v>
+        <v>226.0130748322668</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>48.3</v>
+        <v>92</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,49 +6064,49 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.14235003112806</v>
+        <v>41.84791077368123</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.89318967804405</v>
+        <v>13.36195501029131</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.36950453237601</v>
+        <v>0.6013074832266793</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0006575901762543</v>
+        <v>-0.2875173374959866</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6188</v>
+        <v>6203</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>195.5617991325197</v>
+        <v>213.8791811368409</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>78.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,49 +6117,49 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.85308518753532</v>
+        <v>40.99645254197122</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.61145085278628</v>
+        <v>23.14609788253588</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5561799132519729</v>
+        <v>0.887918113684089</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.6086298896004457</v>
+        <v>-0.614960849074135</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6441</v>
+        <v>6188</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>193.1087327427404</v>
+        <v>195.5617991325197</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.1</v>
+        <v>78.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.60230994100793</v>
+        <v>38.85308512454429</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.44226370108569</v>
+        <v>12.61145086609835</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3108732742740338</v>
+        <v>0.5561799132519729</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1947131816201391</v>
+        <v>-0.6086298895432</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6456</v>
+        <v>6441</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>183.8421715155646</v>
+        <v>193.1087327427404</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69.2</v>
+        <v>23.1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.02463485530316</v>
+        <v>44.60230985716623</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.94812442087138</v>
+        <v>15.44226371493418</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3842171515564554</v>
+        <v>0.3108732742740338</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,11 +6241,11 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.281158212297345</v>
+        <v>-0.1947131815151999</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>34.88244116698111</v>
+        <v>34.88244114876179</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.08204770123904</v>
+        <v>14.08204770279625</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.3514478133846763</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-1.110588742117776</v>
+        <v>-1.11058874218455</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>36.04552503239279</v>
+        <v>36.04552501240816</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.79461697130593</v>
+        <v>13.79461703630051</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.9011436766718172</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2174957300288632</v>
+        <v>-0.2174957300670225</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6276</v>
+        <v>6456</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.1808623211639</v>
+        <v>168.8963704490862</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>25.3</v>
+        <v>69.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.10280730753709</v>
+        <v>44.02463484777198</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.12279136203132</v>
+        <v>17.94812446305059</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5180862321163926</v>
+        <v>0.3896370449086154</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,48 +6400,48 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1480727716840899</v>
+        <v>-1.281158212240107</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6167</v>
+        <v>6287</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>114.1649042058266</v>
+        <v>168.8193640139415</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>11.4</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G113" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.00974407587253</v>
+        <v>51.36725836105252</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.05067925322545</v>
+        <v>0.9513778337062641</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4164904205826616</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,62 +6453,168 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.009135781675858001</v>
+        <v>-0.0065724218287724</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>145.1808623211639</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>34.10280722151373</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>18.12279136203132</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.5180862321163926</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.1480727717413279</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6167</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>114.1649042058266</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>42.00974399030189</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>17.05067926855473</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4164904205826616</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0091357816595084</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
         <v>6236</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>中湛</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
         <v>48.02625827096713</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>9.997409725353366</v>
       </c>
-      <c r="J114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
+      <c r="J116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
         <v>0.3869550343578077</v>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, obv_uptrend</t>
         </is>
